--- a/docs/Smart blok.xlsx
+++ b/docs/Smart blok.xlsx
@@ -2098,7 +2098,7 @@
     <xf numFmtId="41" fontId="45" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="45" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2574,7 +2574,6 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2636,9 +2635,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2647,6 +2643,9 @@
     </xf>
     <xf numFmtId="3" fontId="22" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -29959,7 +29958,7 @@
         <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="B153" s="175" t="s">
+      <c r="B153" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="120" t="s">
@@ -30040,7 +30039,7 @@
         <f t="shared" si="17"/>
         <v>151</v>
       </c>
-      <c r="B154" s="175" t="s">
+      <c r="B154" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C154" s="120" t="s">
@@ -30121,7 +30120,7 @@
         <f t="shared" si="17"/>
         <v>152</v>
       </c>
-      <c r="B155" s="175" t="s">
+      <c r="B155" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C155" s="57" t="s">
@@ -30202,7 +30201,7 @@
         <f t="shared" si="17"/>
         <v>153</v>
       </c>
-      <c r="B156" s="175" t="s">
+      <c r="B156" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C156" s="123" t="s">
@@ -30214,7 +30213,7 @@
       <c r="E156" s="124">
         <v>46228</v>
       </c>
-      <c r="F156" s="176" t="s">
+      <c r="F156" s="175" t="s">
         <v>138</v>
       </c>
       <c r="G156" s="114" t="s">
@@ -30284,7 +30283,7 @@
         <f t="shared" si="17"/>
         <v>154</v>
       </c>
-      <c r="B157" s="175" t="s">
+      <c r="B157" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C157" s="126" t="s">
@@ -30365,7 +30364,7 @@
         <f t="shared" si="17"/>
         <v>155</v>
       </c>
-      <c r="B158" s="175" t="s">
+      <c r="B158" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C158" s="57" t="s">
@@ -30446,7 +30445,7 @@
         <f t="shared" si="17"/>
         <v>156</v>
       </c>
-      <c r="B159" s="175" t="s">
+      <c r="B159" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C159" s="123" t="s">
@@ -30458,7 +30457,7 @@
       <c r="E159" s="124">
         <v>46228</v>
       </c>
-      <c r="F159" s="176" t="s">
+      <c r="F159" s="175" t="s">
         <v>190</v>
       </c>
       <c r="G159" s="114" t="s">
@@ -30528,7 +30527,7 @@
         <f t="shared" si="17"/>
         <v>157</v>
       </c>
-      <c r="B160" s="175" t="s">
+      <c r="B160" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C160" s="123" t="s">
@@ -30540,7 +30539,7 @@
       <c r="E160" s="124">
         <v>46228</v>
       </c>
-      <c r="F160" s="176" t="s">
+      <c r="F160" s="175" t="s">
         <v>190</v>
       </c>
       <c r="G160" s="114" t="s">
@@ -30610,7 +30609,7 @@
         <f t="shared" si="17"/>
         <v>158</v>
       </c>
-      <c r="B161" s="175" t="s">
+      <c r="B161" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C161" s="136" t="s">
@@ -30691,7 +30690,7 @@
         <f t="shared" si="17"/>
         <v>159</v>
       </c>
-      <c r="B162" s="175" t="s">
+      <c r="B162" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C162" s="123" t="s">
@@ -30703,7 +30702,7 @@
       <c r="E162" s="124">
         <v>46229</v>
       </c>
-      <c r="F162" s="176" t="s">
+      <c r="F162" s="175" t="s">
         <v>88</v>
       </c>
       <c r="G162" s="114" t="s">
@@ -30772,7 +30771,7 @@
         <f t="shared" si="17"/>
         <v>160</v>
       </c>
-      <c r="B163" s="175" t="s">
+      <c r="B163" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C163" s="120" t="s">
@@ -30853,7 +30852,7 @@
         <f t="shared" si="17"/>
         <v>161</v>
       </c>
-      <c r="B164" s="175" t="s">
+      <c r="B164" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C164" s="111" t="s">
@@ -30934,7 +30933,7 @@
         <f t="shared" si="17"/>
         <v>162</v>
       </c>
-      <c r="B165" s="175" t="s">
+      <c r="B165" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C165" s="136" t="s">
@@ -31015,7 +31014,7 @@
         <f t="shared" si="17"/>
         <v>163</v>
       </c>
-      <c r="B166" s="175" t="s">
+      <c r="B166" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C166" s="136" t="s">
@@ -31096,7 +31095,7 @@
         <f t="shared" si="17"/>
         <v>164</v>
       </c>
-      <c r="B167" s="175" t="s">
+      <c r="B167" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C167" s="120" t="s">
@@ -31177,7 +31176,7 @@
         <f t="shared" si="17"/>
         <v>165</v>
       </c>
-      <c r="B168" s="175" t="s">
+      <c r="B168" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C168" s="57" t="s">
@@ -31258,7 +31257,7 @@
         <f t="shared" si="17"/>
         <v>166</v>
       </c>
-      <c r="B169" s="175" t="s">
+      <c r="B169" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C169" s="136" t="s">
@@ -31339,7 +31338,7 @@
         <f t="shared" si="17"/>
         <v>167</v>
       </c>
-      <c r="B170" s="175" t="s">
+      <c r="B170" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C170" s="136" t="s">
@@ -31420,7 +31419,7 @@
         <f t="shared" si="17"/>
         <v>168</v>
       </c>
-      <c r="B171" s="175" t="s">
+      <c r="B171" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C171" s="120" t="s">
@@ -31501,7 +31500,7 @@
         <f t="shared" si="17"/>
         <v>169</v>
       </c>
-      <c r="B172" s="175" t="s">
+      <c r="B172" s="57" t="s">
         <v>24</v>
       </c>
       <c r="C172" s="136" t="s">
@@ -31661,12 +31660,12 @@
     <row r="174" spans="1:24">
       <c r="A174" s="49"/>
       <c r="B174" s="57"/>
-      <c r="C174" s="177"/>
-      <c r="D174" s="177"/>
-      <c r="E174" s="177"/>
-      <c r="F174" s="177"/>
-      <c r="G174" s="177"/>
-      <c r="H174" s="178">
+      <c r="C174" s="176"/>
+      <c r="D174" s="176"/>
+      <c r="E174" s="176"/>
+      <c r="F174" s="176"/>
+      <c r="G174" s="176"/>
+      <c r="H174" s="177">
         <f>SUM(H4:H173)</f>
         <v>5323.17600000001</v>
       </c>
@@ -31708,69 +31707,69 @@
         <f>SUM(V4:V173)</f>
         <v>350382127.378304</v>
       </c>
-      <c r="W174" s="179">
+      <c r="W174" s="178">
         <f>SUM(W4:W173)</f>
         <v>2937618614</v>
       </c>
     </row>
     <row r="177" spans="3:19">
-      <c r="C177" s="180" t="s">
+      <c r="C177" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="D177" s="180" t="s">
+      <c r="D177" s="179" t="s">
         <v>200</v>
       </c>
-      <c r="E177" s="180" t="s">
+      <c r="E177" s="179" t="s">
         <v>201</v>
       </c>
-      <c r="F177" s="180" t="s">
+      <c r="F177" s="179" t="s">
         <v>202</v>
       </c>
-      <c r="G177" s="181" t="s">
+      <c r="G177" s="180" t="s">
         <v>203</v>
       </c>
-      <c r="J177" s="182" t="s">
+      <c r="J177" s="181" t="s">
         <v>204</v>
       </c>
-      <c r="K177" s="183"/>
-      <c r="M177" s="184" t="s">
+      <c r="K177" s="182"/>
+      <c r="M177" s="183" t="s">
         <v>205</v>
       </c>
-      <c r="N177" s="185"/>
+      <c r="N177" s="184"/>
     </row>
     <row r="178" spans="3:19">
       <c r="C178" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="D178" s="186">
+      <c r="D178" s="185">
         <f>'Жамол 22-22'!M102+'Жамол 22-22'!M84+'Жамол 22-22'!M72+'Жамол 22-22'!M55+'Жамол 22-22'!M43+'Жамол 22-22'!M33+'Жамол 22-22'!M18+'Жамол 22-22'!M5</f>
         <v>751060559.983104</v>
       </c>
-      <c r="E178" s="186">
+      <c r="E178" s="185">
         <f>'Жамол 22-22'!C5+'Жамол 22-22'!C18+'Жамол 22-22'!C33+'Жамол 22-22'!C43+'Жамол 22-22'!C55+'Жамол 22-22'!C72+'Жамол 22-22'!C84+'Жамол 22-22'!C102</f>
         <v>650896560</v>
       </c>
-      <c r="F178" s="186">
+      <c r="F178" s="185">
         <f>D178-E178</f>
         <v>100163999.983104</v>
       </c>
-      <c r="G178" s="186">
+      <c r="G178" s="185">
         <f>'Жамол 22-22'!K5+'Жамол 22-22'!K18+'Жамол 22-22'!K33+'Жамол 22-22'!K43+'Жамол 22-22'!K55+'Жамол 22-22'!K72+'Жамол 22-22'!K84+'Жамол 22-22'!K102</f>
         <v>613</v>
       </c>
-      <c r="J178" s="187">
+      <c r="J178" s="186">
         <v>46198</v>
       </c>
-      <c r="K178" s="188" t="s">
+      <c r="K178" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L178" s="189">
+      <c r="L178" s="188">
         <v>23328000</v>
       </c>
-      <c r="M178" s="190" t="s">
+      <c r="M178" s="189" t="s">
         <v>206</v>
       </c>
-      <c r="N178" s="190" t="s">
+      <c r="N178" s="189" t="s">
         <v>207</v>
       </c>
       <c r="S178" s="1"/>
@@ -31779,38 +31778,38 @@
       <c r="C179" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="D179" s="186">
+      <c r="D179" s="185">
         <f>'Зафар ога'!M5+'Зафар ога'!M16+'Зафар ога'!M61+'Зафар ога'!M75+'Зафар ога'!M87</f>
         <v>837889920</v>
       </c>
-      <c r="E179" s="186">
+      <c r="E179" s="185">
         <f>'Зафар ога'!C5+'Зафар ога'!C16+'Зафар ога'!C61+'Зафар ога'!C75+'Зафар ога'!C87</f>
         <v>993372920</v>
       </c>
-      <c r="F179" s="186">
+      <c r="F179" s="185">
         <f t="shared" ref="F179:F183" si="27">D179-E179</f>
         <v>-155483000</v>
       </c>
-      <c r="G179" s="186">
+      <c r="G179" s="185">
         <f>'Зафар ога'!K5+'Зафар ога'!K16+'Зафар ога'!K61+'Зафар ога'!K75+'Зафар ога'!K87</f>
         <v>683</v>
       </c>
-      <c r="J179" s="187">
+      <c r="J179" s="186">
         <v>46198</v>
       </c>
-      <c r="K179" s="188" t="s">
+      <c r="K179" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L179" s="189">
+      <c r="L179" s="188">
         <v>45570000</v>
       </c>
-      <c r="M179" s="186">
+      <c r="M179" s="185">
         <f>J174</f>
         <v>3035493990</v>
       </c>
-      <c r="N179" s="186">
+      <c r="N179" s="185">
         <f>L201</f>
-        <v>3371089420</v>
+        <v>3427089420</v>
       </c>
       <c r="S179" s="1"/>
     </row>
@@ -31818,756 +31817,756 @@
       <c r="C180" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="D180" s="186">
+      <c r="D180" s="185">
         <f>'Шохрух ога'!M5+'Шохрух ога'!M24+'Шохрух ога'!M35+'Шохрух ога'!M49+'Шохрух ога'!M61+'Шохрух ога'!M72</f>
         <v>471828039.3792</v>
       </c>
-      <c r="E180" s="186">
+      <c r="E180" s="185">
         <f>'Шохрух ога'!C5+'Шохрух ога'!C24+'Шохрух ога'!C35+'Шохрух ога'!C49+'Шохрух ога'!C61+'Шохрух ога'!C72</f>
         <v>350342440</v>
       </c>
-      <c r="F180" s="186">
+      <c r="F180" s="185">
         <f t="shared" si="27"/>
         <v>121485599.3792</v>
       </c>
-      <c r="G180" s="186">
+      <c r="G180" s="185">
         <f>'Шохрух ога'!K5+'Шохрух ога'!K24+'Шохрух ога'!K35+'Шохрух ога'!K49+'Шохрух ога'!K61+'Шохрух ога'!K72</f>
         <v>386</v>
       </c>
-      <c r="J180" s="187">
+      <c r="J180" s="186">
         <v>46202</v>
       </c>
-      <c r="K180" s="188" t="s">
+      <c r="K180" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L180" s="189">
+      <c r="L180" s="188">
         <v>23965900</v>
       </c>
-      <c r="M180" s="191">
+      <c r="M180" s="190">
         <f>N179-M179</f>
-        <v>335595430</v>
-      </c>
-      <c r="N180" s="192"/>
+        <v>391595430</v>
+      </c>
+      <c r="N180" s="191"/>
       <c r="S180" s="1"/>
     </row>
     <row r="181" spans="3:19">
-      <c r="C181" s="176" t="s">
+      <c r="C181" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="D181" s="186">
+      <c r="D181" s="185">
         <f>'Арслон ога'!M5+'Арслон ога'!M19+'Арслон ога'!M37+'Арслон ога'!M48</f>
         <v>308757600</v>
       </c>
-      <c r="E181" s="186">
+      <c r="E181" s="185">
         <f>'Арслон ога'!C5+'Арслон ога'!C19+'Арслон ога'!C37+'Арслон ога'!C48</f>
         <v>306592600</v>
       </c>
-      <c r="F181" s="186">
+      <c r="F181" s="185">
         <f t="shared" si="27"/>
         <v>2165000</v>
       </c>
-      <c r="G181" s="186">
+      <c r="G181" s="185">
         <f>'Арслон ога'!K5+'Арслон ога'!K19+'Арслон ога'!K37+'Арслон ога'!K48</f>
         <v>247</v>
       </c>
-      <c r="J181" s="187">
+      <c r="J181" s="186">
         <v>46202</v>
       </c>
-      <c r="K181" s="188" t="s">
+      <c r="K181" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L181" s="189">
+      <c r="L181" s="188">
         <v>24624000</v>
       </c>
-      <c r="M181" s="188" t="s">
+      <c r="M181" s="187" t="s">
         <v>114</v>
       </c>
-      <c r="N181" s="188" t="s">
+      <c r="N181" s="187" t="s">
         <v>208</v>
       </c>
       <c r="S181" s="1"/>
     </row>
     <row r="182" spans="3:19">
-      <c r="C182" s="193" t="s">
+      <c r="C182" s="192" t="s">
         <v>80</v>
       </c>
-      <c r="D182" s="186">
+      <c r="D182" s="185">
         <f>'Темур '!M5+'Темур '!M34+'Темур '!M52+'Темур '!M76+'Темур '!M93</f>
         <v>887846400</v>
       </c>
-      <c r="E182" s="186">
+      <c r="E182" s="185">
         <f>'Темур '!C5+'Темур '!C34+'Темур '!C52+'Темур '!C76+'Темур '!C93</f>
         <v>950246400</v>
       </c>
-      <c r="F182" s="186">
+      <c r="F182" s="185">
         <f t="shared" si="27"/>
         <v>-62400000</v>
       </c>
-      <c r="G182" s="186">
+      <c r="G182" s="185">
         <f>'Темур '!K5+'Темур '!K34+'Темур '!K52+'Темур '!K76+'Темур '!K93</f>
         <v>734</v>
       </c>
-      <c r="J182" s="187">
+      <c r="J182" s="186">
         <v>46202</v>
       </c>
-      <c r="K182" s="188" t="s">
+      <c r="K182" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L182" s="189">
+      <c r="L182" s="188">
         <v>47952000</v>
       </c>
-      <c r="M182" s="189">
+      <c r="M182" s="188">
         <v>0</v>
       </c>
-      <c r="N182" s="189">
-        <v>335595430</v>
+      <c r="N182" s="188">
+        <v>391595430</v>
       </c>
     </row>
     <row r="183" spans="3:19">
-      <c r="C183" s="194" t="s">
+      <c r="C183" s="193" t="s">
         <v>95</v>
       </c>
-      <c r="D183" s="186">
+      <c r="D183" s="185">
         <f>'Сардор ога'!M5+'Сардор ога'!M18+'Сардор ога'!M37+'Сардор ога'!M50+'Сардор ога'!M64+'Сардор ога'!M81+'Сардор ога'!M95</f>
         <v>503393600.016</v>
       </c>
-      <c r="E183" s="186">
+      <c r="E183" s="185">
         <f>'Сардор ога'!C5+'Сардор ога'!C18+'Сардор ога'!C37+'Сардор ога'!C50+'Сардор ога'!C64+'Сардор ога'!C81+'Сардор ога'!C95</f>
         <v>604125100</v>
       </c>
-      <c r="F183" s="186">
+      <c r="F183" s="185">
         <f t="shared" si="27"/>
         <v>-100731499.984</v>
       </c>
-      <c r="G183" s="186">
+      <c r="G183" s="185">
         <f>'Сардор ога'!K5+'Сардор ога'!K18+'Сардор ога'!K37+'Сардор ога'!K50+'Сардор ога'!K64+'Сардор ога'!K81+'Сардор ога'!K95</f>
         <v>416</v>
       </c>
-      <c r="J183" s="187">
+      <c r="J183" s="186">
         <v>46203</v>
       </c>
-      <c r="K183" s="188" t="s">
+      <c r="K183" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L183" s="189">
+      <c r="L183" s="188">
         <v>22703000</v>
       </c>
-      <c r="P183" s="179"/>
     </row>
     <row r="184" spans="3:19">
-      <c r="C184" s="195"/>
-      <c r="D184" s="196">
+      <c r="C184" s="194"/>
+      <c r="D184" s="195">
         <f>SUM(D178:D183)</f>
         <v>3760776119.3783</v>
       </c>
-      <c r="E184" s="196">
+      <c r="E184" s="195">
         <f>SUM(E178:E183)</f>
         <v>3855576020</v>
       </c>
-      <c r="F184" s="196">
+      <c r="F184" s="195">
         <f>SUM(F178:F183)</f>
         <v>-94799900.621696</v>
       </c>
-      <c r="G184" s="196">
+      <c r="G184" s="195">
         <f>SUM(G178:G183)</f>
         <v>3079</v>
       </c>
-      <c r="J184" s="187">
+      <c r="J184" s="186">
         <v>46203</v>
       </c>
-      <c r="K184" s="188" t="s">
+      <c r="K184" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L184" s="189">
+      <c r="L184" s="188">
         <v>23872000</v>
       </c>
-      <c r="P184" s="179"/>
+      <c r="P184" s="178"/>
     </row>
     <row r="185" spans="3:19">
-      <c r="D185" s="179"/>
-      <c r="J185" s="187">
+      <c r="D185" s="178"/>
+      <c r="J185" s="186">
         <v>46203</v>
       </c>
-      <c r="K185" s="188" t="s">
+      <c r="K185" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L185" s="189">
+      <c r="L185" s="188">
         <v>50000000</v>
       </c>
-      <c r="M185" s="179"/>
+      <c r="M185" s="178"/>
+      <c r="P185" s="178"/>
     </row>
     <row r="186" spans="3:19">
-      <c r="E186" s="179"/>
-      <c r="J186" s="187">
+      <c r="E186" s="178"/>
+      <c r="J186" s="186">
         <v>46204</v>
       </c>
-      <c r="K186" s="188" t="s">
+      <c r="K186" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L186" s="189">
+      <c r="L186" s="188">
         <v>25231000</v>
       </c>
     </row>
     <row r="187" spans="3:19">
-      <c r="E187" s="179"/>
-      <c r="J187" s="187">
+      <c r="E187" s="178"/>
+      <c r="J187" s="186">
         <v>46205</v>
       </c>
-      <c r="K187" s="188" t="s">
+      <c r="K187" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L187" s="189">
+      <c r="L187" s="188">
         <v>67737600</v>
       </c>
     </row>
     <row r="188" spans="3:19">
-      <c r="E188" s="179"/>
-      <c r="J188" s="187">
+      <c r="E188" s="178"/>
+      <c r="J188" s="186">
         <v>46205</v>
       </c>
-      <c r="K188" s="188" t="s">
+      <c r="K188" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L188" s="189">
+      <c r="L188" s="188">
         <v>72394560</v>
       </c>
     </row>
     <row r="189" spans="3:19">
-      <c r="D189" s="179"/>
-      <c r="E189" s="179"/>
-      <c r="F189" s="179"/>
-      <c r="G189" s="179"/>
-      <c r="J189" s="187">
+      <c r="D189" s="178"/>
+      <c r="E189" s="178"/>
+      <c r="F189" s="178"/>
+      <c r="G189" s="178"/>
+      <c r="J189" s="186">
         <v>46205</v>
       </c>
-      <c r="K189" s="188" t="s">
+      <c r="K189" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L189" s="189">
+      <c r="L189" s="188">
         <v>73872000</v>
       </c>
     </row>
     <row r="190" spans="3:19">
-      <c r="E190" s="179"/>
-      <c r="J190" s="187">
+      <c r="E190" s="178"/>
+      <c r="J190" s="186">
         <v>46206</v>
       </c>
-      <c r="K190" s="188" t="s">
+      <c r="K190" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L190" s="189">
+      <c r="L190" s="188">
         <v>47934720</v>
       </c>
     </row>
     <row r="191" spans="3:19">
-      <c r="E191" s="179"/>
-      <c r="J191" s="187">
+      <c r="E191" s="178"/>
+      <c r="J191" s="186">
         <v>46206</v>
       </c>
-      <c r="K191" s="188" t="s">
+      <c r="K191" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L191" s="189">
+      <c r="L191" s="188">
         <v>49904640</v>
       </c>
     </row>
     <row r="192" spans="3:19">
-      <c r="E192" s="179"/>
-      <c r="J192" s="187">
+      <c r="E192" s="178"/>
+      <c r="J192" s="186">
         <v>46206</v>
       </c>
-      <c r="K192" s="188" t="s">
+      <c r="K192" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L192" s="189">
+      <c r="L192" s="188">
         <v>50000000</v>
       </c>
     </row>
     <row r="193" spans="5:18">
-      <c r="E193" s="179"/>
-      <c r="J193" s="187">
+      <c r="E193" s="178"/>
+      <c r="J193" s="186">
         <v>46206</v>
       </c>
-      <c r="K193" s="188" t="s">
+      <c r="K193" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L193" s="189">
+      <c r="L193" s="188">
         <v>506000000</v>
       </c>
     </row>
     <row r="194" spans="5:18">
-      <c r="E194" s="179"/>
-      <c r="J194" s="187">
+      <c r="E194" s="178"/>
+      <c r="J194" s="186">
         <v>46206</v>
       </c>
-      <c r="K194" s="188" t="s">
+      <c r="K194" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L194" s="189">
+      <c r="L194" s="188">
         <v>890000000</v>
       </c>
     </row>
     <row r="195" spans="5:18">
-      <c r="E195" s="179"/>
-      <c r="J195" s="187">
+      <c r="E195" s="178"/>
+      <c r="J195" s="186">
         <v>46206</v>
       </c>
-      <c r="K195" s="188" t="s">
+      <c r="K195" s="187" t="s">
         <v>114</v>
       </c>
-      <c r="L195" s="189">
+      <c r="L195" s="188">
         <v>6000000</v>
       </c>
     </row>
     <row r="196" spans="5:18">
-      <c r="E196" s="179"/>
-      <c r="J196" s="187">
+      <c r="E196" s="178"/>
+      <c r="J196" s="186">
         <v>46213</v>
       </c>
-      <c r="K196" s="188" t="s">
+      <c r="K196" s="187" t="s">
         <v>209</v>
       </c>
-      <c r="L196" s="189">
+      <c r="L196" s="188">
         <v>50000000</v>
       </c>
       <c r="M196" s="119"/>
       <c r="N196" s="118"/>
     </row>
     <row r="197" spans="5:18">
-      <c r="E197" s="179"/>
-      <c r="J197" s="187">
+      <c r="E197" s="178"/>
+      <c r="J197" s="186">
         <v>46213</v>
       </c>
-      <c r="K197" s="188" t="s">
+      <c r="K197" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L197" s="189">
+      <c r="L197" s="188">
         <v>300000000</v>
       </c>
     </row>
     <row r="198" spans="5:18">
-      <c r="E198" s="179"/>
-      <c r="J198" s="187">
+      <c r="E198" s="178"/>
+      <c r="J198" s="186">
         <v>46220</v>
       </c>
-      <c r="K198" s="188" t="s">
+      <c r="K198" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L198" s="189">
+      <c r="L198" s="188">
         <v>626000000</v>
       </c>
-      <c r="Q198" s="197"/>
     </row>
     <row r="199" spans="5:18">
-      <c r="E199" s="179"/>
-      <c r="J199" s="187">
+      <c r="E199" s="178"/>
+      <c r="J199" s="186">
         <v>46227</v>
       </c>
-      <c r="K199" s="188" t="s">
+      <c r="K199" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L199" s="189">
+      <c r="L199" s="188">
         <v>200000000</v>
       </c>
-      <c r="Q199" s="198"/>
+      <c r="Q199" s="196"/>
     </row>
     <row r="200" spans="5:18">
-      <c r="E200" s="179"/>
-      <c r="J200" s="187">
+      <c r="E200" s="178"/>
+      <c r="J200" s="186">
         <v>46231</v>
       </c>
-      <c r="K200" s="188" t="s">
+      <c r="K200" s="187" t="s">
         <v>31</v>
       </c>
-      <c r="L200" s="189">
+      <c r="L200" s="188">
         <v>200000000</v>
       </c>
-      <c r="Q200" s="199"/>
+      <c r="Q200" s="197"/>
     </row>
     <row r="201" spans="5:18">
-      <c r="J201" s="200" t="s">
+      <c r="J201" s="198" t="s">
         <v>210</v>
       </c>
-      <c r="K201" s="201"/>
-      <c r="L201" s="202">
-        <f>L178+L179+L180+L181+L182+L183+L184+L185+L186+L187+L188+L189+L190+L191+L192+L193+L194+L197+L198+L199+L200</f>
-        <v>3371089420</v>
-      </c>
-      <c r="Q201" s="203"/>
+      <c r="K201" s="199"/>
+      <c r="L201" s="200">
+        <f>SUM(L178:L200)</f>
+        <v>3427089420</v>
+      </c>
+      <c r="Q201" s="201"/>
+    </row>
+    <row r="202" spans="5:18">
+      <c r="Q202" s="202"/>
     </row>
     <row r="204" spans="5:18">
-      <c r="M204" s="179"/>
-    </row>
-    <row r="206" spans="5:18">
-      <c r="Q206" s="179"/>
+      <c r="M204" s="178"/>
     </row>
     <row r="207" spans="5:18">
-      <c r="G207" s="197"/>
-      <c r="H207" s="197"/>
-      <c r="I207" s="197"/>
-      <c r="J207" s="197"/>
-      <c r="K207" s="204"/>
-      <c r="N207" s="205"/>
-      <c r="O207" s="205"/>
-      <c r="R207" s="197"/>
+      <c r="G207" s="196"/>
+      <c r="H207" s="196"/>
+      <c r="I207" s="196"/>
+      <c r="J207" s="196"/>
+      <c r="K207" s="203"/>
+      <c r="N207" s="204"/>
+      <c r="O207" s="204"/>
+      <c r="Q207" s="178"/>
+      <c r="R207" s="196"/>
     </row>
     <row r="208" spans="5:18">
-      <c r="G208" s="206"/>
-      <c r="H208" s="199"/>
-      <c r="I208" s="199"/>
-      <c r="J208" s="199"/>
-      <c r="K208" s="199"/>
-      <c r="N208" s="207"/>
+      <c r="G208" s="205"/>
+      <c r="H208" s="201"/>
+      <c r="I208" s="201"/>
+      <c r="J208" s="201"/>
+      <c r="K208" s="201"/>
+      <c r="N208" s="206"/>
       <c r="O208" s="118"/>
-      <c r="R208" s="198"/>
+      <c r="R208" s="197"/>
     </row>
     <row r="209" spans="7:21">
-      <c r="G209" s="206"/>
-      <c r="H209" s="199"/>
-      <c r="I209" s="199"/>
-      <c r="J209" s="199"/>
-      <c r="K209" s="199"/>
-      <c r="N209" s="207"/>
+      <c r="G209" s="205"/>
+      <c r="H209" s="201"/>
+      <c r="I209" s="201"/>
+      <c r="J209" s="201"/>
+      <c r="K209" s="201"/>
+      <c r="N209" s="206"/>
       <c r="O209" s="118"/>
-      <c r="R209" s="199"/>
+      <c r="R209" s="201"/>
     </row>
     <row r="210" spans="7:21">
-      <c r="G210" s="206"/>
-      <c r="H210" s="199"/>
-      <c r="I210" s="199"/>
-      <c r="J210" s="199"/>
-      <c r="K210" s="199"/>
-      <c r="N210" s="207"/>
+      <c r="G210" s="205"/>
+      <c r="H210" s="201"/>
+      <c r="I210" s="201"/>
+      <c r="J210" s="201"/>
+      <c r="K210" s="201"/>
+      <c r="N210" s="206"/>
       <c r="O210" s="118"/>
-      <c r="R210" s="197"/>
+      <c r="R210" s="196"/>
     </row>
     <row r="211" spans="7:21">
-      <c r="G211" s="206"/>
-      <c r="H211" s="199"/>
-      <c r="I211" s="199"/>
-      <c r="J211" s="199"/>
-      <c r="K211" s="199"/>
-      <c r="N211" s="207"/>
+      <c r="G211" s="205"/>
+      <c r="H211" s="201"/>
+      <c r="I211" s="201"/>
+      <c r="J211" s="201"/>
+      <c r="K211" s="201"/>
+      <c r="N211" s="206"/>
       <c r="O211" s="118"/>
     </row>
     <row r="212" spans="7:21">
-      <c r="H212" s="199"/>
-      <c r="I212" s="199"/>
-      <c r="J212" s="199"/>
-      <c r="K212" s="199"/>
-      <c r="N212" s="207"/>
+      <c r="H212" s="201"/>
+      <c r="I212" s="201"/>
+      <c r="J212" s="201"/>
+      <c r="K212" s="201"/>
+      <c r="N212" s="206"/>
       <c r="O212" s="118"/>
-      <c r="Q212" s="197"/>
     </row>
     <row r="213" spans="7:21">
-      <c r="G213" s="198"/>
-      <c r="H213" s="199"/>
-      <c r="I213" s="199"/>
-      <c r="J213" s="199"/>
-      <c r="K213" s="199"/>
-      <c r="N213" s="207"/>
+      <c r="G213" s="197"/>
+      <c r="H213" s="201"/>
+      <c r="I213" s="201"/>
+      <c r="J213" s="201"/>
+      <c r="K213" s="201"/>
+      <c r="N213" s="206"/>
       <c r="O213" s="118"/>
-      <c r="Q213" s="198"/>
+      <c r="Q213" s="196"/>
     </row>
     <row r="214" spans="7:21">
-      <c r="H214" s="199"/>
-      <c r="I214" s="199"/>
-      <c r="J214" s="199"/>
-      <c r="K214" s="199"/>
-      <c r="N214" s="207"/>
+      <c r="H214" s="201"/>
+      <c r="I214" s="201"/>
+      <c r="J214" s="201"/>
+      <c r="K214" s="201"/>
+      <c r="N214" s="206"/>
       <c r="O214" s="118"/>
-      <c r="Q214" s="199"/>
+      <c r="Q214" s="197"/>
     </row>
     <row r="215" spans="7:21">
-      <c r="H215" s="179"/>
-      <c r="N215" s="207"/>
+      <c r="H215" s="178"/>
+      <c r="N215" s="206"/>
       <c r="O215" s="118"/>
-      <c r="Q215" s="203"/>
+      <c r="Q215" s="201"/>
     </row>
     <row r="216" spans="7:21">
-      <c r="I216" s="179"/>
-      <c r="N216" s="207"/>
+      <c r="I216" s="178"/>
+      <c r="N216" s="206"/>
       <c r="O216" s="118"/>
+      <c r="Q216" s="202"/>
     </row>
     <row r="217" spans="7:21">
-      <c r="I217" s="179"/>
-      <c r="N217" s="207"/>
+      <c r="I217" s="178"/>
+      <c r="N217" s="206"/>
       <c r="O217" s="118"/>
     </row>
     <row r="218" spans="7:21">
-      <c r="I218" s="179"/>
-      <c r="N218" s="207"/>
+      <c r="I218" s="178"/>
+      <c r="N218" s="206"/>
       <c r="O218" s="118"/>
     </row>
     <row r="220" spans="7:21">
-      <c r="M220" s="208"/>
-      <c r="Q220" s="179"/>
+      <c r="M220" s="207"/>
     </row>
     <row r="221" spans="7:21">
-      <c r="G221" s="197"/>
-      <c r="H221" s="197"/>
-      <c r="I221" s="197"/>
-      <c r="J221" s="197"/>
-      <c r="K221" s="204"/>
-      <c r="N221" s="205"/>
-      <c r="O221" s="205"/>
-      <c r="R221" s="197"/>
-      <c r="T221" s="197"/>
-      <c r="U221" s="197"/>
+      <c r="G221" s="196"/>
+      <c r="H221" s="196"/>
+      <c r="I221" s="196"/>
+      <c r="J221" s="196"/>
+      <c r="K221" s="203"/>
+      <c r="N221" s="204"/>
+      <c r="O221" s="204"/>
+      <c r="Q221" s="178"/>
+      <c r="R221" s="196"/>
+      <c r="T221" s="196"/>
+      <c r="U221" s="196"/>
     </row>
     <row r="222" spans="7:21">
-      <c r="G222" s="206"/>
-      <c r="H222" s="199"/>
-      <c r="I222" s="199"/>
-      <c r="J222" s="199"/>
-      <c r="K222" s="199"/>
-      <c r="N222" s="207"/>
+      <c r="G222" s="205"/>
+      <c r="H222" s="201"/>
+      <c r="I222" s="201"/>
+      <c r="J222" s="201"/>
+      <c r="K222" s="201"/>
+      <c r="N222" s="206"/>
       <c r="O222" s="118"/>
-      <c r="R222" s="198"/>
-      <c r="T222" s="206"/>
-      <c r="U222" s="199"/>
+      <c r="R222" s="197"/>
+      <c r="T222" s="205"/>
+      <c r="U222" s="201"/>
     </row>
     <row r="223" spans="7:21">
-      <c r="G223" s="206"/>
-      <c r="H223" s="199"/>
-      <c r="I223" s="199"/>
-      <c r="J223" s="199"/>
-      <c r="K223" s="199"/>
-      <c r="N223" s="207"/>
+      <c r="G223" s="205"/>
+      <c r="H223" s="201"/>
+      <c r="I223" s="201"/>
+      <c r="J223" s="201"/>
+      <c r="K223" s="201"/>
+      <c r="N223" s="206"/>
       <c r="O223" s="118"/>
-      <c r="R223" s="199"/>
-      <c r="T223" s="206"/>
-      <c r="U223" s="199"/>
+      <c r="R223" s="201"/>
+      <c r="T223" s="205"/>
+      <c r="U223" s="201"/>
     </row>
     <row r="224" spans="7:21">
-      <c r="G224" s="206"/>
-      <c r="H224" s="199"/>
-      <c r="I224" s="199"/>
-      <c r="J224" s="199"/>
-      <c r="K224" s="199"/>
-      <c r="N224" s="207"/>
+      <c r="G224" s="205"/>
+      <c r="H224" s="201"/>
+      <c r="I224" s="201"/>
+      <c r="J224" s="201"/>
+      <c r="K224" s="201"/>
+      <c r="N224" s="206"/>
       <c r="O224" s="118"/>
-      <c r="Q224" s="197"/>
-      <c r="R224" s="197"/>
-      <c r="T224" s="206"/>
-      <c r="U224" s="199"/>
+      <c r="R224" s="196"/>
+      <c r="T224" s="205"/>
+      <c r="U224" s="201"/>
     </row>
     <row r="225" spans="7:21">
-      <c r="G225" s="206"/>
-      <c r="H225" s="199"/>
-      <c r="I225" s="199"/>
-      <c r="J225" s="199"/>
-      <c r="K225" s="199"/>
-      <c r="N225" s="207"/>
+      <c r="G225" s="205"/>
+      <c r="H225" s="201"/>
+      <c r="I225" s="201"/>
+      <c r="J225" s="201"/>
+      <c r="K225" s="201"/>
+      <c r="N225" s="206"/>
       <c r="O225" s="118"/>
-      <c r="Q225" s="198"/>
-      <c r="T225" s="206"/>
-      <c r="U225" s="199"/>
+      <c r="Q225" s="196"/>
+      <c r="T225" s="205"/>
+      <c r="U225" s="201"/>
     </row>
     <row r="226" spans="7:21">
-      <c r="G226" s="206"/>
-      <c r="H226" s="199"/>
-      <c r="I226" s="199"/>
-      <c r="J226" s="199"/>
-      <c r="K226" s="199"/>
-      <c r="N226" s="207"/>
+      <c r="G226" s="205"/>
+      <c r="H226" s="201"/>
+      <c r="I226" s="201"/>
+      <c r="J226" s="201"/>
+      <c r="K226" s="201"/>
+      <c r="N226" s="206"/>
       <c r="O226" s="118"/>
-      <c r="Q226" s="199"/>
-      <c r="T226" s="206"/>
-      <c r="U226" s="199"/>
+      <c r="Q226" s="197"/>
+      <c r="T226" s="205"/>
+      <c r="U226" s="201"/>
     </row>
     <row r="227" spans="7:21">
-      <c r="G227" s="198"/>
-      <c r="H227" s="199"/>
-      <c r="I227" s="199"/>
-      <c r="J227" s="199"/>
-      <c r="K227" s="199"/>
-      <c r="N227" s="207"/>
+      <c r="G227" s="197"/>
+      <c r="H227" s="201"/>
+      <c r="I227" s="201"/>
+      <c r="J227" s="201"/>
+      <c r="K227" s="201"/>
+      <c r="N227" s="206"/>
       <c r="O227" s="118"/>
-      <c r="Q227" s="203"/>
-      <c r="T227" s="198"/>
-      <c r="U227" s="199"/>
+      <c r="Q227" s="201"/>
+      <c r="T227" s="197"/>
+      <c r="U227" s="201"/>
     </row>
     <row r="228" spans="7:21">
-      <c r="H228" s="199"/>
-      <c r="I228" s="199"/>
-      <c r="J228" s="199"/>
-      <c r="K228" s="199"/>
-      <c r="N228" s="207"/>
+      <c r="H228" s="201"/>
+      <c r="I228" s="201"/>
+      <c r="J228" s="201"/>
+      <c r="K228" s="201"/>
+      <c r="N228" s="206"/>
       <c r="O228" s="118"/>
-      <c r="U228" s="199"/>
+      <c r="Q228" s="202"/>
+      <c r="U228" s="201"/>
     </row>
     <row r="229" spans="7:21">
-      <c r="H229" s="179"/>
-      <c r="N229" s="207"/>
+      <c r="H229" s="178"/>
+      <c r="N229" s="206"/>
       <c r="O229" s="118"/>
-      <c r="U229" s="179"/>
+      <c r="U229" s="178"/>
     </row>
     <row r="230" spans="7:21">
-      <c r="I230" s="179"/>
-      <c r="N230" s="207"/>
+      <c r="I230" s="178"/>
+      <c r="N230" s="206"/>
       <c r="O230" s="118"/>
     </row>
     <row r="231" spans="7:21">
-      <c r="I231" s="179"/>
-      <c r="N231" s="207"/>
+      <c r="I231" s="178"/>
+      <c r="N231" s="206"/>
       <c r="O231" s="118"/>
     </row>
     <row r="232" spans="7:21">
-      <c r="I232" s="179"/>
-      <c r="N232" s="207"/>
+      <c r="I232" s="178"/>
+      <c r="N232" s="206"/>
       <c r="O232" s="118"/>
-      <c r="Q232" s="179"/>
     </row>
     <row r="233" spans="7:21">
-      <c r="G233" s="197"/>
-      <c r="H233" s="197"/>
-      <c r="I233" s="197"/>
-      <c r="J233" s="197"/>
-      <c r="K233" s="204"/>
-      <c r="N233" s="205"/>
-      <c r="O233" s="205"/>
-      <c r="R233" s="197"/>
-      <c r="T233" s="197"/>
-      <c r="U233" s="197"/>
+      <c r="G233" s="196"/>
+      <c r="H233" s="196"/>
+      <c r="I233" s="196"/>
+      <c r="J233" s="196"/>
+      <c r="K233" s="203"/>
+      <c r="N233" s="204"/>
+      <c r="O233" s="204"/>
+      <c r="Q233" s="178"/>
+      <c r="R233" s="196"/>
+      <c r="T233" s="196"/>
+      <c r="U233" s="196"/>
     </row>
     <row r="234" spans="7:21">
-      <c r="G234" s="206"/>
-      <c r="H234" s="199"/>
-      <c r="I234" s="199"/>
-      <c r="J234" s="199"/>
-      <c r="K234" s="199"/>
-      <c r="N234" s="207"/>
+      <c r="G234" s="205"/>
+      <c r="H234" s="201"/>
+      <c r="I234" s="201"/>
+      <c r="J234" s="201"/>
+      <c r="K234" s="201"/>
+      <c r="N234" s="206"/>
       <c r="O234" s="118"/>
-      <c r="R234" s="198"/>
-      <c r="T234" s="206"/>
-      <c r="U234" s="199"/>
+      <c r="R234" s="197"/>
+      <c r="T234" s="205"/>
+      <c r="U234" s="201"/>
     </row>
     <row r="235" spans="7:21">
-      <c r="G235" s="206"/>
-      <c r="H235" s="199"/>
-      <c r="I235" s="199"/>
-      <c r="J235" s="199"/>
-      <c r="K235" s="199"/>
-      <c r="N235" s="207"/>
+      <c r="G235" s="205"/>
+      <c r="H235" s="201"/>
+      <c r="I235" s="201"/>
+      <c r="J235" s="201"/>
+      <c r="K235" s="201"/>
+      <c r="N235" s="206"/>
       <c r="O235" s="118"/>
-      <c r="R235" s="199"/>
-      <c r="T235" s="206"/>
-      <c r="U235" s="199"/>
+      <c r="R235" s="201"/>
+      <c r="T235" s="205"/>
+      <c r="U235" s="201"/>
     </row>
     <row r="236" spans="7:21">
-      <c r="G236" s="206"/>
-      <c r="H236" s="199"/>
-      <c r="I236" s="199"/>
-      <c r="J236" s="199"/>
-      <c r="K236" s="199"/>
-      <c r="N236" s="207"/>
+      <c r="G236" s="205"/>
+      <c r="H236" s="201"/>
+      <c r="I236" s="201"/>
+      <c r="J236" s="201"/>
+      <c r="K236" s="201"/>
+      <c r="N236" s="206"/>
       <c r="O236" s="118"/>
-      <c r="Q236" s="197"/>
-      <c r="R236" s="197"/>
-      <c r="T236" s="206"/>
-      <c r="U236" s="199"/>
+      <c r="R236" s="196"/>
+      <c r="T236" s="205"/>
+      <c r="U236" s="201"/>
     </row>
     <row r="237" spans="7:21">
-      <c r="G237" s="206"/>
-      <c r="H237" s="199"/>
-      <c r="I237" s="199"/>
-      <c r="J237" s="199"/>
-      <c r="K237" s="199"/>
-      <c r="N237" s="207"/>
+      <c r="G237" s="205"/>
+      <c r="H237" s="201"/>
+      <c r="I237" s="201"/>
+      <c r="J237" s="201"/>
+      <c r="K237" s="201"/>
+      <c r="N237" s="206"/>
       <c r="O237" s="118"/>
-      <c r="Q237" s="198"/>
-      <c r="T237" s="206"/>
-      <c r="U237" s="199"/>
+      <c r="Q237" s="196"/>
+      <c r="T237" s="205"/>
+      <c r="U237" s="201"/>
     </row>
     <row r="238" spans="7:21">
-      <c r="G238" s="206"/>
-      <c r="H238" s="199"/>
-      <c r="I238" s="199"/>
-      <c r="J238" s="199"/>
-      <c r="K238" s="199"/>
-      <c r="N238" s="207"/>
+      <c r="G238" s="205"/>
+      <c r="H238" s="201"/>
+      <c r="I238" s="201"/>
+      <c r="J238" s="201"/>
+      <c r="K238" s="201"/>
+      <c r="N238" s="206"/>
       <c r="O238" s="118"/>
-      <c r="Q238" s="199"/>
-      <c r="T238" s="206"/>
-      <c r="U238" s="199"/>
+      <c r="Q238" s="197"/>
+      <c r="T238" s="205"/>
+      <c r="U238" s="201"/>
     </row>
     <row r="239" spans="7:21">
-      <c r="G239" s="198"/>
-      <c r="H239" s="199"/>
-      <c r="I239" s="199"/>
-      <c r="J239" s="199"/>
-      <c r="K239" s="199"/>
-      <c r="N239" s="207"/>
+      <c r="G239" s="197"/>
+      <c r="H239" s="201"/>
+      <c r="I239" s="201"/>
+      <c r="J239" s="201"/>
+      <c r="K239" s="201"/>
+      <c r="N239" s="206"/>
       <c r="O239" s="118"/>
-      <c r="T239" s="198"/>
-      <c r="U239" s="199"/>
+      <c r="Q239" s="201"/>
+      <c r="T239" s="197"/>
+      <c r="U239" s="201"/>
     </row>
     <row r="240" spans="7:21">
-      <c r="H240" s="199"/>
-      <c r="I240" s="199"/>
-      <c r="J240" s="199"/>
-      <c r="K240" s="199"/>
-      <c r="N240" s="207"/>
+      <c r="H240" s="201"/>
+      <c r="I240" s="201"/>
+      <c r="J240" s="201"/>
+      <c r="K240" s="201"/>
+      <c r="N240" s="206"/>
       <c r="O240" s="118"/>
-      <c r="U240" s="199"/>
+      <c r="U240" s="201"/>
     </row>
     <row r="241" spans="7:21">
-      <c r="H241" s="179"/>
-      <c r="N241" s="207"/>
+      <c r="H241" s="178"/>
+      <c r="N241" s="206"/>
       <c r="O241" s="118"/>
-      <c r="U241" s="179"/>
+      <c r="U241" s="178"/>
     </row>
     <row r="242" spans="7:21">
-      <c r="I242" s="179"/>
-      <c r="N242" s="207"/>
+      <c r="I242" s="178"/>
+      <c r="N242" s="206"/>
       <c r="O242" s="118"/>
     </row>
     <row r="243" spans="7:21">
-      <c r="I243" s="179"/>
-      <c r="N243" s="207"/>
+      <c r="I243" s="178"/>
+      <c r="N243" s="206"/>
       <c r="O243" s="118"/>
     </row>
     <row r="244" spans="7:21">
-      <c r="I244" s="179"/>
-      <c r="N244" s="207"/>
+      <c r="I244" s="178"/>
+      <c r="N244" s="206"/>
       <c r="O244" s="118"/>
     </row>
     <row r="245" spans="7:21">
-      <c r="G245" s="197"/>
-      <c r="H245" s="197"/>
-      <c r="I245" s="197"/>
-      <c r="J245" s="197"/>
-      <c r="K245" s="204"/>
-      <c r="N245" s="205"/>
-      <c r="O245" s="205"/>
-      <c r="R245" s="197"/>
-      <c r="T245" s="197"/>
-      <c r="U245" s="197"/>
+      <c r="G245" s="196"/>
+      <c r="H245" s="196"/>
+      <c r="I245" s="196"/>
+      <c r="J245" s="196"/>
+      <c r="K245" s="203"/>
+      <c r="N245" s="204"/>
+      <c r="O245" s="204"/>
+      <c r="R245" s="196"/>
+      <c r="T245" s="196"/>
+      <c r="U245" s="196"/>
     </row>
     <row r="246" spans="7:21">
-      <c r="G246" s="206"/>
-      <c r="H246" s="199"/>
-      <c r="I246" s="199"/>
-      <c r="J246" s="199"/>
-      <c r="K246" s="199"/>
-      <c r="N246" s="207"/>
+      <c r="G246" s="205"/>
+      <c r="H246" s="201"/>
+      <c r="I246" s="201"/>
+      <c r="J246" s="201"/>
+      <c r="K246" s="201"/>
+      <c r="N246" s="206"/>
       <c r="O246" s="118"/>
-      <c r="R246" s="198"/>
-      <c r="T246" s="206"/>
-      <c r="U246" s="199"/>
+      <c r="R246" s="197"/>
+      <c r="T246" s="205"/>
+      <c r="U246" s="201"/>
     </row>
     <row r="247" spans="7:21">
-      <c r="G247" s="206"/>
-      <c r="H247" s="199"/>
-      <c r="I247" s="199"/>
-      <c r="J247" s="199"/>
-      <c r="K247" s="199"/>
-      <c r="N247" s="207"/>
+      <c r="G247" s="205"/>
+      <c r="H247" s="201"/>
+      <c r="I247" s="201"/>
+      <c r="J247" s="201"/>
+      <c r="K247" s="201"/>
+      <c r="N247" s="206"/>
       <c r="O247" s="118"/>
-      <c r="R247" s="199"/>
-      <c r="T247" s="206"/>
-      <c r="U247" s="199"/>
+      <c r="R247" s="201"/>
+      <c r="T247" s="205"/>
+      <c r="U247" s="201"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:X174" etc:filterBottomFollowUsedRange="0">
